--- a/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -673,7 +673,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A library catalog app needs to pull out specific letters from a book title code to build a short reference tag.
+```python
 word = "Python"
 print(word[0], word[2])
 ```
@@ -755,7 +756,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A signup form for a food-delivery app cleans up an email address a user pasted in with stray spaces.
+```python
 messy = "   asha@email.com   "
 print(messy.strip())
 ```
@@ -837,7 +839,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A shopping cart checkout screen needs to show the order total formatted to two decimal places.
+```python
 price = 49.5
 print(f"Total: {price:.2f}")
 ```
@@ -919,7 +922,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A banking app masks a customer's phone number and only displays the last four digits for verification.
+```python
 phone_number = "9876543210"
 last_four = phone_number[-4:]
 print(last_four)
@@ -1085,7 +1089,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A social media app auto-generates a hashtag from a list of keywords a user tags on their post.
+```python
 hashtag_words = ["handmade", "gifts", "pune"]
 hashtag = "#" + "".join(word.title() for word in hashtag_words)
 print(hashtag)
@@ -1168,7 +1173,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A word-puzzle app counts how many times a target letter appears in a given sentence.
+```python
 sentence = "she sells sea shells"
 print(sentence.count("s"))
 ```
@@ -1250,7 +1256,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A contact-export feature in a chat app joins a customer's profile fields into one line of text for a CSV file.
+```python
 values = ["Asha", 20, "Pune"]
 print(", ".join(values))
 ```
@@ -1332,7 +1339,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A profile page on a fitness app can display a user's bio line using three different string-formatting styles.
+```python
 name = "Asha"
 age = 20
 line1 = f"{name} is {age} years old."
@@ -1518,7 +1526,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which line correctly stores the text It's a sunny day without causing a syntax problem?</t>
+          <t>A weather app needs to store the forecast note "It's a sunny day" without breaking the code.
+Which line correctly stores the text It's a sunny day without causing a syntax problem?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1596,7 +1605,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A username field on a signup form needs to check how many characters a user has typed so far.
+```python
 word = "Python"
 print(len(word))
 ```
@@ -1678,7 +1688,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A comment box on a forum app needs to detect whether a user submitted an empty comment.
+```python
 blank = ""
 ```
 What is `len(blank)`, and how does blank behave in an if condition?</t>
@@ -1759,7 +1770,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why is it important that a string is described as an 'ordered' sequence of characters rather than just a collection of characters?</t>
+          <t>A search feature on an e-commerce site relies on being able to find the exact position of a character within a product code.
+Why is it important that a string is described as an 'ordered' sequence of characters rather than just a collection of characters?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1837,7 +1849,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A text-editor app tries to preview a character at a position beyond the end of a short filename.
+```python
 word = "Python"
 print(word[10])
 ```
@@ -1919,7 +1932,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A puzzle app builds a shortened code by picking every alternate letter from a word.
+```python
 word = "Python"
 print(word[::2])
 ```
@@ -2001,7 +2015,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A file-preview tool tries to slice a filename using an end index far beyond the string's actual length.
+```python
 word = "Python"
 print(word[2:100])
 ```
@@ -2083,7 +2098,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A text-processing tool slices a word using a start index that comes after the end index.
+```python
 word = "Python"
 print(word[4:2])
 ```
@@ -2165,7 +2181,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A messaging app shows a quick preview of the last couple of characters typed in a chat box.
+```python
 word = "Python"
 print(word[-1], word[-2])
 ```
@@ -2247,7 +2264,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A ticketing app extracts a short substring from a booking reference code to display on the ticket stub.
+```python
 word = "Python"
 print(word[2:5])
 ```
@@ -2430,7 +2448,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A password-strength checker in a banking app reverses a user's input string to run a palindrome-style validation check.
+```python
 word = "Python"
 print(word[::-1])
 ```
@@ -2512,7 +2531,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A text editor tries to fix a typo by directly overwriting the first letter of a stored word.
+```python
 word = "Python"
 word[0] = "J"
 ```
@@ -2594,7 +2614,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A shipping label app splits a tracking code into a prefix and suffix to print on two separate lines.
+```python
 word = "Python"
 print(word[:3], word[3:])
 ```
@@ -2676,7 +2697,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A login form tries to normalize a username to uppercase before saving it, but a developer forgets to store the result.
+```python
 name = "asha"
 name.upper()
 print(name)
@@ -2759,7 +2781,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A debugging session in a text-processing tool checks whether editing a word actually changes the original string object in memory.
+```python
 word = "Python"
 first_id = id(word)
 word = "J" + word[1:]
@@ -2844,7 +2867,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why does Python's string immutability make strings safe to use as dictionary keys and to share across a program?</t>
+          <t>A user-profile system stores account settings in a dictionary keyed by usernames shared across multiple parts of the app.
+Why does Python's string immutability make strings safe to use as dictionary keys and to share across a program?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2922,7 +2946,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A blogging platform formats an article heading so each word starts with a capital letter.
+```python
 text = "hello world"
 print(text.title())
 ```
@@ -3004,7 +3029,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A recipe app lets a user swap one ingredient for another throughout a saved recipe note.
+```python
 sentence = "I like tea"
 print(sentence.replace("tea", "coffee"))
 ```
@@ -3086,7 +3112,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A social media app splits a comma-separated hashtag line into individual tags for storage.
+```python
 tags_line = "handmade,gifts,pune"
 tags = tags_line.split(",")
 print(tags)
@@ -3169,7 +3196,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A document-formatting tool offers two similar-looking options for capitalizing a heading.
+```python
 text = "hello world"
 ```
 What is the difference between `text.capitalize()` and `text.title()`?</t>
@@ -3351,7 +3379,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>```python
+          <t>A signup form normalizes an email address by trimming stray spaces and lowering the case before saving it.
+```python
 raw = "  ASHA@EMAIL.COM  "
 clean = raw.strip().lower()
 print(clean)
@@ -3434,7 +3463,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>```python
+          <t>A sports news app needs to reformat a player's name into properly capitalized title case for a headline.
+```python
 name = "sachin tendulkar"
 words = name.split()
 joined = " ".join(words)
@@ -3518,7 +3548,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A form-validation script tries to trim whitespace from user input but forgets to save the trimmed result back.
+```python
 raw = "  Hello  "
 raw.strip()
 print(raw)
@@ -3601,7 +3632,8 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>```python
+          <t>A voice-assistant app breaks a spoken sentence into individual words for further processing.
+```python
 sentence = "Python is fun"
 print(sentence.split())
 ```
@@ -3683,7 +3715,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>```python
+          <t>A search-tag feature in an app joins separate keywords into one dash-separated string for a URL slug.
+```python
 words = ["Python", "is", "fun"]
 print("-".join(words))
 ```
@@ -3765,7 +3798,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>```python
+          <t>A signup form quickly checks whether a typed email address looks valid by testing for the "@" symbol.
+```python
 email = "asha@email.com"
 print("@" in email)
 ```
@@ -3847,7 +3881,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A signup form searches for the "@" symbol in a user's typed email to locate the domain part.
+```python
 email = "asha gmail.com"
 print(email.find("@"))
 ```
@@ -3929,7 +3964,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A receipt-printing feature in a cafe app aligns an item name and its price into neat columns.
+```python
 print(f"{'Tea':&lt;10}{45:&gt;8}")
 ```
 What does this produce, and what do &lt; and &gt; control?</t>
@@ -4010,7 +4046,8 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>```python
+          <t>A file-upload system checks a filename's extension and prefix before accepting a document.
+```python
 filename = "report.pdf"
 print(filename.endswith(".pdf"), filename.startswith("Rep"))
 ```
@@ -4092,7 +4129,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A text-search tool in a notes app needs to look for a character that does not appear in the note, and the choice of method matters for how errors are handled.
+```python
 text = "hello world"
 ```
 What is the key difference between `text.find("z")` and `text.index("z")` here?</t>

--- a/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 5.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 5.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 5.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 5.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>A collection of unrelated values with no order</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>A single number with decimals</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>An ordered sequence of characters wrapped in quotes</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>A collection of unrelated values with no order</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>A type that can only hold digits</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -726,26 +726,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>P y</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>y h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>y t</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>P y</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>P t</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>y h</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -814,21 +814,21 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>asha@`email.com`</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asha@`email.com`   </t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t xml:space="preserve">   asha@`email.com`</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>asha@`email.com`</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asha@`email.com`   </t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -892,26 +892,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Total: 49.50</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Total: 49.5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Total: 49.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Total: 50</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Total: 49.50</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Total: 49.500</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Total: 49.5</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -976,26 +976,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>9876</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>6543</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>3210</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1059,26 +1059,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>JPython, because the J is inserted at the start without removing anything</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Python, because slicing fails silently</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>JPython, because the J is inserted at the start without removing anything</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
+          <t>Error, because this is the same as direct mutation</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>Jython, because a brand new string is built and the variable is repointed to it</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Error, because this is the same as direct mutation</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1143,26 +1143,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>#Handmade Gifts Pune</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>#handmadegiftspune</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>#HandmadeGiftsPune</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>#handmade,gifts,pune</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>#Handmade Gifts Pune</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>#handmadegiftspune</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1231,21 +1231,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1309,26 +1309,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>It silently skips the integer and prints 'Asha, Pune'</t>
+          <t>It raises a `TypeError` because `join()` requires all items to be strings</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>It prints 'Asha, 20, Pune' normally</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>It converts 20 to '20' automatically and prints fine</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>It prints 'Asha, 20, Pune' normally</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>It raises a `TypeError` because `join()` requires all items to be strings</t>
+          <t>It silently skips the integer and prints just 'Asha, Pune' instead</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Only line1 actually produces the correct output; the other two lines simply raise errors</t>
+          <t>line2 and line3 produce completely identical output, but line1 adds some extra spaces</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>line2 and line3 produce completely identical output, but line1 adds some extra spaces</t>
+          <t>line3 fails to run at all because the % operator cannot be used with strings</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>line3 fails to run at all because the % operator cannot be used with strings</t>
+          <t>Only line1 actually produces the correct output here; the other two lines simply raise errors instead every time</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1575,17 +1575,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>`sentence = ""`It's a sunny day""</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>sentence = It's a sunny day</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>`sentence = 'It'`s a sunny day'</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>sentence = It's a sunny day</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>`sentence = ""`It's a sunny day""</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1658,26 +1658,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Error, `len()` does not work on strings</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1740,26 +1740,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>0, and it is falsy</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0, and it is truthy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>1, and it is truthy</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0, and it is truthy</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Error, an empty string is invalid</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0, and it is falsy</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1819,26 +1819,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Python strings are actually stored unordered internally</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Order only ever matters for numbers, never for text</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Order is what makes indexing, slicing, and position-based operations possible</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Order genuinely has no real effect on how strings behave</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Python strings are actually stored unordered internally</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Order only ever matters for numbers, never for text</t>
+          <t>Order genuinely has no real effect on how strings behave in Python at all</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1907,21 +1907,21 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>It raises an `IndexError` because the index is out of range</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>It silently prints an empty string back</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>It silently prints the value `None` instead</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>It silently prints an empty string back</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>It raises an `IndexError` because the index is out of range</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1985,26 +1985,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>Pto</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>yhn</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>Pyth</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Pto</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>yhn</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2068,26 +2068,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>It returns an empty string</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>It returns 'thon', stopping safely at the end of the string</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>It raises an `IndexError`, same as direct indexing would</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>It returns the string padded with empty characters</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>It returns an empty string</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2151,22 +2151,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>It raises an error</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>An empty string</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>tho printed here</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>ohty printed</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>An empty string</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>tho printed here</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>It raises an error</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2234,26 +2234,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>h o</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>P y</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>o n</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>n o</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>P y</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>h o</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2317,22 +2317,22 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>ytho</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>thon</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>tho</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Pyth</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>tho</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>ytho</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -2501,26 +2501,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>nohtyP</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>P</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>nohtyP</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2584,26 +2584,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>It creates an entirely new separate variable called `word[0]`</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>It silently does nothing at all here and no error occurs</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>It successfully changes the value of word to 'Jython'</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>It raises a `TypeError` because strings do not support item assignment</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>It creates an entirely new separate variable called `word[0]`</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2667,26 +2667,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Pyt hon</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Python Python</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Pyt on</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Pyth on</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Pyt on</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Pyt hon</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Python Python</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>An error, because `upper()` requires reassignment</t>
+          <t>ASHA, because `upper()` changes the original</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2761,16 +2761,16 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>An error occurs, because `upper()` technically needs reassignment</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>asha, because the returned result was never assigned back to name</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ASHA, because `upper()` changes the original</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2837,26 +2837,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>`True`, because `id()` always returns the same value for strings</t>
+          <t>`False`, proving a new string object was created and the variable repointed to it</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>An error occurs, because `id()` cannot be used on strings at all</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>`True`, because `id()` always returns the exact same value for every string</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>`True`, proving that the string was edited in place directly</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>An error occurs, because `id()` cannot be used on strings at all</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>`False`, proving a new string object was created and the variable repointed to it</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2921,21 +2921,21 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>It makes strings the only data type ever allowed as dictionary keys</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>It guarantees the value can never be silently changed by other code that holds a reference to it</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>It makes strings the only data type ever allowed as dictionary keys</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Immutability has no real practical benefit, it is just a quirk of Python</t>
+          <t>Immutability has no real practical benefit at all, it is just an odd quirk of Python</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2999,26 +2999,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>HELLO WORLD</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Hello world</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>Hello World</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>HELLO WORLD</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>hello world</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Hello world</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3082,26 +3082,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>I like coffee</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>I like tea</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>I like coffee</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>I like teacoffee</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3166,26 +3166,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>'handmade,gifts,pune'</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>['handmade', 'gifts', 'pune']</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>['handmade,gifts,pune']</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>handmade gifts pune</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>'handmade,gifts,pune'</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>['handmade', 'gifts', 'pune']</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>`title()` removes all spaces from the string entirely, while `capitalize()` does not</t>
+          <t>`capitalize()` capitalises every word; `title()` capitalises only the first word</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>`capitalize()` capitalises every word; `title()` capitalises only the first word</t>
+          <t>`capitalize()` capitalises only the first letter of the string; `title()` capitalises the first letter of each word</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>`capitalize()` capitalises only the first letter of the string; `title()` capitalises the first letter of each word</t>
+          <t>`title()` removes all the spaces from the string entirely, while `capitalize()` genuinely never does that</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3433,26 +3433,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>asha@`email.com`</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  asha@`email.com`  </t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Error, methods cannot be chained on strings</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>ASHA@`EMAIL.COM`</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>asha@`email.com`</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3518,26 +3518,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>sachin tendulkar</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Sachin Tendulkar</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Sachin tendulkar</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>SACHIN TENDULKAR</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>sachin tendulkar</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3602,26 +3602,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>'  Hello  ', because the result of `strip()` was never stored back into raw</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>'Hello', because `strip()` always mutates the original</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>'Hello' printed, but with extra spaces added on</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>'  Hello  ', because the result of `strip()` was never stored back into raw</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>An error occurs, because `strip()` technically requires arguments</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3685,26 +3685,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Error, `split()` requires an argument</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>['Python is fun']</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>['Python', 'is', 'fun']</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>['P', 'y', 't', 'h', 'o', 'n']</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Error, `split()` requires an argument</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>['Python', 'is', 'fun']</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3773,17 +3773,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>Python is fun</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>-Python-is-fun-</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>PythonisFun</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Python is fun</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -3851,26 +3851,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>`False`</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>`True`</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3944,16 +3944,16 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>`None`</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4016,26 +4016,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>&lt; centres the text in the field and &gt; reverses it entirely</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>&lt; left-aligns within the given width and &gt; right-aligns within the given width</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>&lt; and &gt; both simply mean 'round to that many decimal places'</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>&lt; and &gt; are only ever valid when formatting integers, not strings</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>&lt; and &gt; both simply mean 'round to that many decimal places'</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>&lt; centres the text in the field and &gt; reverses it entirely</t>
-        </is>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4099,26 +4099,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>`True` `True`</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>`False` `False`</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>`False` `True`</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>`True` `False`</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>`False` `False`</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>`False` `True`</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>`True` `True`</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4186,21 +4186,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>`find()` raises an error here; `index()` simply returns -1 instead</t>
+          <t>`find()` returns -1; `index()` raises a `ValueError` when the substring is missing</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>`find()` returns -1; `index()` raises a `ValueError` when the substring is missing</t>
+          <t>They behave in exactly the same identical way in this situation</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>They behave in exactly the same identical way in this situation</t>
+          <t>`find()` raises an error in this case; `index()` simply returns -1 instead</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -2794,7 +2794,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>`id()` returns an object's identity in memory; since reassigning word points it at a brand new string object rather than editing the old one in place, first_id and second_id differ, so this prints `False`, proving the original string was never mutated.</t>
+          <t>`id()` returns an object's identity in memory; since reassigning word points it at a brand new string object rather than editing the old one in place, `first_id` and `second_id` differ, so this prints `False`, proving the original string was never mutated.</t>
         </is>
       </c>
       <c r="D6" t="n">

--- a/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -1347,7 +1347,7 @@
 line2 = "{} is {} years old.".format(name, age)
 line3 = "%s is %d years old." % (name, age)
 ```
-Which statement about line1, line2, and line3 is correct?</t>
+Which statement about `line1`, `line2`, and `line3` is correct?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>line2 and line3 produce completely identical output, but line1 adds some extra spaces</t>
+          <t>`line2` and `line3` produce completely identical output, but `line1` adds some extra spaces</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>line3 fails to run at all because the % operator cannot be used with strings</t>
+          <t>`line3` fails to run at all because the `%` operator cannot be used with strings</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Only line1 actually produces the correct output here; the other two lines simply raise errors instead every time</t>
+          <t>Only `line1` actually produces the correct output here; the other two lines simply raise errors instead every time</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1527,7 +1527,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>A weather app needs to store the forecast note "It's a sunny day" without breaking the code.
-Which line correctly stores the text It's a sunny day without causing a syntax problem?</t>
+Which line correctly stores the text `It's a sunny day` without causing a syntax problem?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1575,17 +1575,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>`sentence = ""`It's a sunny day""</t>
+          <t>`sentence = ""It's a sunny day""`</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>sentence = It's a sunny day</t>
+          <t>`sentence = It's a sunny day`</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>`sentence = 'It'`s a sunny day'</t>
+          <t>`sentence = 'It's a sunny day'`</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -3968,12 +3968,12 @@
 ```python
 print(f"{'Tea':&lt;10}{45:&gt;8}")
 ```
-What does this produce, and what do &lt; and &gt; control?</t>
+What does this produce, and what do `&lt;` and `&gt;` control?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The &lt; after the width sets left alignment, padding 'Tea' with spaces on the right out to 10 characters, while &gt; sets right alignment, padding 45 with spaces on the left out to 8 characters, together forming a neatly aligned column layout.</t>
+          <t>The `&lt;` after the width sets left alignment, padding 'Tea' with spaces on the right out to 10 characters, while `&gt;` sets right alignment, padding 45 with spaces on the left out to 8 characters, together forming a neatly aligned column layout.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>&lt; centres the text in the field and &gt; reverses it entirely</t>
+          <t>`&lt;` centres the text in the field and `&gt;` reverses it entirely</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>&lt; left-aligns within the given width and &gt; right-aligns within the given width</t>
+          <t>`&lt;` left-aligns within the given width and `&gt;` right-aligns within the given width</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>&lt; and &gt; both simply mean 'round to that many decimal places'</t>
+          <t>`&lt;` and `&gt;` both simply mean 'round to that many decimal places'</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>&lt; and &gt; are only ever valid when formatting integers, not strings</t>
+          <t>`&lt;` and `&gt;` are only ever valid when formatting integers, not strings</t>
         </is>
       </c>
       <c r="Q9" t="n">

--- a/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rea3750b2a86545aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rf7079d5482df4aa4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,12 +30,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -49,7 +59,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -75,6 +85,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -391,55 +407,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="11" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="11" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="11" t="str">
         <x:v>explanation</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="11" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="E1" s="11" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="F1" s="11" t="str">
         <x:v>difficulty</x:v>
       </x:c>
-      <x:c r="G1" s="8" t="str">
+      <x:c r="G1" s="11" t="str">
         <x:v>bloomTaxonomy</x:v>
       </x:c>
-      <x:c r="H1" s="8" t="str">
+      <x:c r="H1" s="11" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="8" t="str">
+      <x:c r="I1" s="11" t="str">
         <x:v>subjects</x:v>
       </x:c>
-      <x:c r="J1" s="8" t="str">
+      <x:c r="J1" s="11" t="str">
         <x:v>topics</x:v>
       </x:c>
-      <x:c r="K1" s="8" t="str">
+      <x:c r="K1" s="11" t="str">
         <x:v>subTopics</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="L1" s="11" t="str">
         <x:v>companies</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
+      <x:c r="M1" s="11" t="str">
         <x:v>option1</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="N1" s="11" t="str">
         <x:v>option2</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="O1" s="11" t="str">
         <x:v>option3</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="P1" s="11" t="str">
         <x:v>option4</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
+      <x:c r="Q1" s="11" t="str">
         <x:v>answer</x:v>
       </x:c>
     </x:row>
@@ -818,16 +834,16 @@
       </x:c>
       <x:c r="L8" s="9"/>
       <x:c r="M8" s="9" t="str">
-        <x:v>`Asha scored score marks`</x:v>
+        <x:v>`Asha scored score points`</x:v>
       </x:c>
       <x:c r="N8" s="9" t="str">
-        <x:v>`Asha scored 87 marks`</x:v>
+        <x:v>`Asha scored 87 points`</x:v>
       </x:c>
       <x:c r="O8" s="9" t="str">
-        <x:v>`name scored score marks`</x:v>
+        <x:v>`name scored score points`</x:v>
       </x:c>
       <x:c r="P8" s="9" t="str">
-        <x:v>`{name} scored {score} marks`</x:v>
+        <x:v>`{name} scored {score} points`</x:v>
       </x:c>
       <x:c r="Q8" s="9" t="n">
         <x:v>2</x:v>
@@ -1621,12 +1637,12 @@
         <x:v>Python - MCQ - 5.2.12</x:v>
       </x:c>
       <x:c r="B23" s="9" t="str">
-        <x:v>A registration form checks whether an ID contains only digits.
-```python
-student_id = "2026A"
-ok = student_id.isdigit()
-```
-What value will the form store in `ok`, and why?</x:v>
+        <x:v>A registration service checks whether an account ID contains only digits.
+```python
+account_id = "2026A"
+ok = account_id.isdigit()
+```
+Which value will the service store in `ok`, and why?</x:v>
       </x:c>
       <x:c r="C23" s="9" t="str">
         <x:v>`isdigit()` returns True only when all characters are digits. The letter `A` makes the result False.</x:v>
@@ -1677,15 +1693,15 @@
         <x:v>Python - MCQ - 5.2.13</x:v>
       </x:c>
       <x:c r="B24" s="9" t="str">
-        <x:v>A CSV importer receives one row of marks.
-```python
-row = "Asha,87,Pass"
+        <x:v>A shipment importer receives one CSV row.
+```python
+row = "BX104,87,Ready"
 fields = row.split(",")
 ```
-What fields will the importer extract?</x:v>
+Which fields will the importer extract?</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>Splitting on comma separates the text into three parts: name, marks, and result.</x:v>
+        <x:v>Splitting on the comma returns three strings: the shipment code, numeric-looking text, and status. `split()` does not convert `87` to an integer.</x:v>
       </x:c>
       <x:c r="D24" s="9" t="n">
         <x:v>1</x:v>
@@ -1713,16 +1729,16 @@
       </x:c>
       <x:c r="L24" s="9"/>
       <x:c r="M24" s="9" t="str">
-        <x:v>`['Asha', '87', 'Pass']`</x:v>
+        <x:v>`['BX104', '87', 'Ready']`</x:v>
       </x:c>
       <x:c r="N24" s="9" t="str">
-        <x:v>`['Asha,87,Pass']`</x:v>
+        <x:v>`['BX104,87,Ready']`</x:v>
       </x:c>
       <x:c r="O24" s="9" t="str">
-        <x:v>`Asha 87 Pass`</x:v>
+        <x:v>`BX104 87 Ready`</x:v>
       </x:c>
       <x:c r="P24" s="9" t="str">
-        <x:v>`['Asha', 87, 'Pass']` — incorrectly converting numeric-looking text during `split()`</x:v>
+        <x:v>`['BX104', 87, 'Ready']` — incorrectly converting numeric-looking text during `split()`</x:v>
       </x:c>
       <x:c r="Q24" s="9" t="n">
         <x:v>1</x:v>
@@ -2002,7 +2018,7 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="P29" s="9" t="str">
-        <x:v>`@college.edu`</x:v>
+        <x:v>The literal string `@example.com`, rather than a Boolean validation result</x:v>
       </x:c>
       <x:c r="Q29" s="9" t="n">
         <x:v>2</x:v>
@@ -2181,12 +2197,12 @@
         <x:v>Python - MCQ - 5.2.22</x:v>
       </x:c>
       <x:c r="B33" s="9" t="str">
-        <x:v>A marks dashboard formats a percentage to one decimal place.
+        <x:v>A performance dashboard formats a score percentage to one decimal place.
 ```python
 percent = 87.456
 label = f"Score: {percent:.1f}%"
 ```
-What label will the dashboard show?</x:v>
+Which label will the dashboard show?</x:v>
       </x:c>
       <x:c r="C33" s="9" t="str">
         <x:v>`:.1f` formats the number with one digit after the decimal point, rounding 87.456 to 87.5.</x:v>
@@ -2414,7 +2430,7 @@
 What email ID will the service generate?</x:v>
       </x:c>
       <x:c r="C37" s="9" t="str">
-        <x:v>The first and last names are converted to lowercase and inserted with the roll number into the email template.</x:v>
+        <x:v>The first and last names are converted to lowercase and inserted with the numeric user ID into the `@example.com` email template.</x:v>
       </x:c>
       <x:c r="D37" s="9" t="n">
         <x:v>1</x:v>
@@ -2442,16 +2458,16 @@
       </x:c>
       <x:c r="L37" s="9"/>
       <x:c r="M37" s="9" t="str">
-        <x:v>`asha.rao@college.edu27`</x:v>
+        <x:v>`asha.rao@example.com27`</x:v>
       </x:c>
       <x:c r="N37" s="9" t="str">
-        <x:v>`Asha.Rao27@college.edu`</x:v>
+        <x:v>`Asha.Rao27@example.com`</x:v>
       </x:c>
       <x:c r="O37" s="9" t="str">
-        <x:v>`first.last27@college.edu`</x:v>
+        <x:v>`first.last27@example.com`</x:v>
       </x:c>
       <x:c r="P37" s="9" t="str">
-        <x:v>`asha.rao27@college.edu`</x:v>
+        <x:v>`asha.rao27@example.com`</x:v>
       </x:c>
       <x:c r="Q37" s="9" t="n">
         <x:v>4</x:v>
@@ -2685,7 +2701,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cf40682dff54279"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd481b453914b4d5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 5 - Strings/Unit 5 - Strings - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="Rf7079d5482df4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 5" sheetId="1" r:id="R5da7ed932e9d44ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,12 +30,32 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -59,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -90,6 +110,18 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -407,55 +439,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" customHeight="1">
-      <x:c r="A1" s="11" t="str">
+      <x:c r="A1" s="15" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="B1" s="11" t="str">
+      <x:c r="B1" s="15" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="C1" s="11" t="str">
+      <x:c r="C1" s="15" t="str">
         <x:v>explanation</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="D1" s="15" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="E1" s="11" t="str">
+      <x:c r="E1" s="15" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="str">
+      <x:c r="F1" s="15" t="str">
         <x:v>difficulty</x:v>
       </x:c>
-      <x:c r="G1" s="11" t="str">
+      <x:c r="G1" s="15" t="str">
         <x:v>bloomTaxonomy</x:v>
       </x:c>
-      <x:c r="H1" s="11" t="str">
+      <x:c r="H1" s="15" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="11" t="str">
+      <x:c r="I1" s="15" t="str">
         <x:v>subjects</x:v>
       </x:c>
-      <x:c r="J1" s="11" t="str">
+      <x:c r="J1" s="15" t="str">
         <x:v>topics</x:v>
       </x:c>
-      <x:c r="K1" s="11" t="str">
+      <x:c r="K1" s="15" t="str">
         <x:v>subTopics</x:v>
       </x:c>
-      <x:c r="L1" s="11" t="str">
+      <x:c r="L1" s="15" t="str">
         <x:v>companies</x:v>
       </x:c>
-      <x:c r="M1" s="11" t="str">
+      <x:c r="M1" s="15" t="str">
         <x:v>option1</x:v>
       </x:c>
-      <x:c r="N1" s="11" t="str">
+      <x:c r="N1" s="15" t="str">
         <x:v>option2</x:v>
       </x:c>
-      <x:c r="O1" s="11" t="str">
+      <x:c r="O1" s="15" t="str">
         <x:v>option3</x:v>
       </x:c>
-      <x:c r="P1" s="11" t="str">
+      <x:c r="P1" s="15" t="str">
         <x:v>option4</x:v>
       </x:c>
-      <x:c r="Q1" s="11" t="str">
+      <x:c r="Q1" s="15" t="str">
         <x:v>answer</x:v>
       </x:c>
     </x:row>
@@ -645,7 +677,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
         <x:v>apply</x:v>
@@ -702,7 +734,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
         <x:v>apply</x:v>
@@ -815,7 +847,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
         <x:v>apply</x:v>
@@ -984,7 +1016,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1092,7 +1124,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
         <x:v>apply</x:v>
@@ -1148,7 +1180,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1430,7 +1462,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
         <x:v>apply</x:v>
@@ -1486,7 +1518,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
         <x:v>apply</x:v>
@@ -1542,7 +1574,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
         <x:v>apply</x:v>
@@ -1654,7 +1686,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F23" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G23" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2102,7 +2134,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2158,7 +2190,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
         <x:v>apply</x:v>
@@ -2270,7 +2302,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G34" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2326,7 +2358,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F35" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G35" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2381,7 +2413,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F36" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G36" s="9" t="str">
         <x:v>apply</x:v>
@@ -2529,21 +2561,15 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A39" s="9" t="str">
         <x:v>Python - MCQ - 5.2.28</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>A search bar normalizes both the saved product name and the user's query before comparing them.
-```python
-product = "Wireless Mouse"
-query = " wireless mouse "
-match = product.lower() == query.strip().lower()
-```
-What value will the search bar store in `match`?</x:v>
+        <x:v>A username repair tries `name[0] = name[0].upper()` and fails because strings are immutable. What is the smallest correct change?</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>The product becomes `wireless mouse`. The query is stripped and lowercased to the same text, so the comparison is True.</x:v>
+        <x:v>Build a new string from the uppercase first character and the unchanged remainder, then assign it back.</x:v>
       </x:c>
       <x:c r="D39" s="9" t="n">
         <x:v>1</x:v>
@@ -2552,7 +2578,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F39" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G39" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2567,39 +2593,34 @@
         <x:v>strings-and-text</x:v>
       </x:c>
       <x:c r="K39" s="9" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>string-immutability</x:v>
       </x:c>
       <x:c r="L39" s="9"/>
       <x:c r="M39" s="9" t="str">
-        <x:v>False</x:v>
+        <x:v>Convert the name to an integer before changing its first character</x:v>
       </x:c>
       <x:c r="N39" s="9" t="str">
-        <x:v>True</x:v>
+        <x:v>Use `name = name[0].upper() + name[1:]`</x:v>
       </x:c>
       <x:c r="O39" s="9" t="str">
-        <x:v>An error</x:v>
+        <x:v>Call `name.sort()` and assume sorting capitalizes the first character</x:v>
       </x:c>
       <x:c r="P39" s="9" t="str">
-        <x:v>`Wireless Mouse`</x:v>
+        <x:v>Delete every character after index 0, which changes the requirement rather than repairing it</x:v>
       </x:c>
       <x:c r="Q39" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A40" s="9" t="str">
         <x:v>Python - MCQ - 5.2.29</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>A log parser extracts the status after the colon in a log entry.
-```python
-entry = "status:SUCCESS"
-status = entry.split(":")[1].lower()
-```
-What status value will the parser store?</x:v>
+        <x:v>Compare two slug implementations. A chains `strip().lower().replace(' ', '-')`; B loops through indexes and edits characters in place. Which is the better implementation for a Python string?</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>Splitting on `:` gives `['status', 'SUCCESS']`. Index 1 selects `SUCCESS`, and `lower()` converts it to `success`.</x:v>
+        <x:v>A uses string methods that return new strings and directly expresses each required transformation. B conflicts with string immutability.</x:v>
       </x:c>
       <x:c r="D40" s="9" t="n">
         <x:v>1</x:v>
@@ -2611,7 +2632,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G40" s="9" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H40" s="9" t="str">
         <x:v>python - Set 2</x:v>
@@ -2623,39 +2644,34 @@
         <x:v>strings-and-text</x:v>
       </x:c>
       <x:c r="K40" s="9" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>string-methods</x:v>
       </x:c>
       <x:c r="L40" s="9"/>
       <x:c r="M40" s="9" t="str">
-        <x:v>`success`</x:v>
+        <x:v>A, because it expresses the transformations clearly and respects string immutability</x:v>
       </x:c>
       <x:c r="N40" s="9" t="str">
-        <x:v>`status`</x:v>
+        <x:v>B, because indexed assignment is the standard way to mutate Python strings</x:v>
       </x:c>
       <x:c r="O40" s="9" t="str">
-        <x:v>`SUCCESS`</x:v>
+        <x:v>B, because calling more than one string method always raises an exception</x:v>
       </x:c>
       <x:c r="P40" s="9" t="str">
-        <x:v>`status:success`</x:v>
+        <x:v>Both are equivalent because string methods modify the original string in place — this choice incorrectly combines two separate operations instead of applying only the stated one</x:v>
       </x:c>
       <x:c r="Q40" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A41" s="9" t="str">
         <x:v>Python - MCQ - 5.2.30</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>A form should accept names only when the user enters at least one non-space character.
-```python
-name = "   "
-valid = len(name.strip()) &gt; 0
-```
-What value will the form store in `valid`, and why?</x:v>
+        <x:v>A validator should accept codes of exactly eight characters, but uses `len(code) &gt; 8`. Which boundary test best exposes the bug?</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>`strip()` removes all spaces, leaving an empty string. Its length is 0, so the comparison is False.</x:v>
+        <x:v>A code of length exactly eight should pass the requirement but fails the `&gt; 8` implementation.</x:v>
       </x:c>
       <x:c r="D41" s="9" t="n">
         <x:v>1</x:v>
@@ -2679,20 +2695,20 @@
         <x:v>strings-and-text</x:v>
       </x:c>
       <x:c r="K41" s="9" t="str">
-        <x:v>practical-text-processing</x:v>
+        <x:v>string-validation</x:v>
       </x:c>
       <x:c r="L41" s="9"/>
       <x:c r="M41" s="9" t="str">
-        <x:v>True, because the original string contains three characters even though all three are removed by `strip()`</x:v>
+        <x:v>Test a nine-character code, which both the intended and faulty conditions accept</x:v>
       </x:c>
       <x:c r="N41" s="9" t="str">
-        <x:v>False, because only spaces remain after validation</x:v>
+        <x:v>Test a valid code containing exactly eight characters</x:v>
       </x:c>
       <x:c r="O41" s="9" t="str">
-        <x:v>An error, because spaces cannot be stripped</x:v>
+        <x:v>Test only an empty string and infer all other lengths from that result</x:v>
       </x:c>
       <x:c r="P41" s="9" t="str">
-        <x:v>True, because `strip()` adds characters</x:v>
+        <x:v>Change the code to uppercase without testing its length</x:v>
       </x:c>
       <x:c r="Q41" s="9" t="n">
         <x:v>2</x:v>
@@ -2701,7 +2717,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd481b453914b4d5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ec55adc33cf4b7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>